--- a/Design-Files/ArmBand-Contrrol-Board/Project Outputs for ArmBand-Control-Board/ArmBand-Control-Board.xlsx
+++ b/Design-Files/ArmBand-Contrrol-Board/Project Outputs for ArmBand-Control-Board/ArmBand-Control-Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Design-Files\ArmBand-Contrrol-Board\Project Outputs for ArmBand-Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA3B895F-05B3-4351-9889-EF85FEDAA75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5E630DB-813B-4AAA-B68E-0B4EFC15ACF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13620" yWindow="0" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17010" yWindow="240" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="266">
   <si>
     <t>Component list</t>
   </si>
@@ -62,9 +62,6 @@
     <t>None</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>Designator</t>
   </si>
   <si>
@@ -230,7 +227,7 @@
     <t>CAP CER 2.2UF 25V X5R 0402</t>
   </si>
   <si>
-    <t>0402 1 nF 25 V ±10 % Tolerance X7R SMT Multilayer Ceramic Capacitor, CAP CER 1000PF 25V X7R 0402</t>
+    <t>CAP CER 1000PF 25V X7R 0402</t>
   </si>
   <si>
     <t>CAP CER 0.8PF 50V C0G/NP0 0402</t>
@@ -248,13 +245,13 @@
     <t>Clamshell 22 Double-sided contacts/up and down connection Surface Mount 0.5mm SMD,P=0.5mm FFC/FPC Connectors ROHS</t>
   </si>
   <si>
-    <t>2A Surface Mount Square Pins 2mm 4mm -40℃~+105℃ 1 8 2mm 1x8P SMD,P=2mm Pin Headers ROHS</t>
+    <t>CONN HEADER VERT 8POS 2.54MM</t>
   </si>
   <si>
     <t>CONN FPC/FFC 12POS .5MM</t>
   </si>
   <si>
-    <t>4 POS 2.54mm Pin Header Male single row Right Angle SMD</t>
+    <t>CONN HEADER VERT 4POS 2.54MM</t>
   </si>
   <si>
     <t>FIXED IND 2.2UH 1.5A 160MOHM SMD</t>
@@ -284,10 +281,10 @@
     <t>LED RED CLEAR CHIP SMD</t>
   </si>
   <si>
-    <t>0.1W ±5% ±1500ppm/℃ 25mΩ 0603 Chip Resistor - Surface Mount ROHS</t>
-  </si>
-  <si>
-    <t>RES SMD 1K OHM 5% 1/10W 0402, RES 1K OHM 5% 1/16W 0402</t>
+    <t>RES SMD 25m Ohms 125mW 0805</t>
+  </si>
+  <si>
+    <t>RES 1K OHM 5% 1/16W 0402</t>
   </si>
   <si>
     <t>RES SMD 10K OHM 1% 1/16W 0402</t>
@@ -371,13 +368,13 @@
     <t>F0504-H-22-20T-R</t>
   </si>
   <si>
-    <t>SMD Header 1x8</t>
+    <t>HDR1X8</t>
   </si>
   <si>
     <t>FH34SRJ-12S-0.5SH(50)</t>
   </si>
   <si>
-    <t>HDR1X4 SMD</t>
+    <t>HDR1X4</t>
   </si>
   <si>
     <t>MAKK2016T2R2M</t>
@@ -401,12 +398,15 @@
     <t>LED 0402</t>
   </si>
   <si>
+    <t>RES 0805</t>
+  </si>
+  <si>
+    <t>Res0402</t>
+  </si>
+  <si>
     <t>Res0603</t>
   </si>
   <si>
-    <t>Res0402</t>
-  </si>
-  <si>
     <t>Solder Bridge</t>
   </si>
   <si>
@@ -470,15 +470,12 @@
     <t>GRM155R61E225KE11D</t>
   </si>
   <si>
-    <t>CC0402JRNPO9BN200, CC0402KRX7R8BB102</t>
+    <t>CC0402KRX7R8BB102</t>
   </si>
   <si>
     <t>GJM1555C1HR80WB01D</t>
   </si>
   <si>
-    <t>1220-1108G0Z090CR02</t>
-  </si>
-  <si>
     <t>MGFL2012F100MT-LF</t>
   </si>
   <si>
@@ -494,10 +491,7 @@
     <t>XZMDK68W-2</t>
   </si>
   <si>
-    <t>RTT03R025JTP</t>
-  </si>
-  <si>
-    <t>ERJ-2GEJ102X, RC0402JR-071KL</t>
+    <t>RC0402JR-071KL</t>
   </si>
   <si>
     <t>RC0402FR-0710KL</t>
@@ -542,6 +536,9 @@
     <t>VRD2828PTX</t>
   </si>
   <si>
+    <t>#Column Name Error:' Alternate Part No</t>
+  </si>
+  <si>
     <t>Manufacturer</t>
   </si>
   <si>
@@ -569,10 +566,7 @@
     <t>XFCN</t>
   </si>
   <si>
-    <t>Wcon</t>
-  </si>
-  <si>
-    <t>RTLECS</t>
+    <t>Wurth Electronics</t>
   </si>
   <si>
     <t>TDK</t>
@@ -590,10 +584,7 @@
     <t>SunLED</t>
   </si>
   <si>
-    <t>Relac</t>
-  </si>
-  <si>
-    <t>Panasonic, Yageo</t>
+    <t>UNI-Royal Elec</t>
   </si>
   <si>
     <t>FOJAN</t>
@@ -668,9 +659,6 @@
     <t>0.8pF</t>
   </si>
   <si>
-    <t>PH254P1x12SMRA-100</t>
-  </si>
-  <si>
     <t>2.2uH</t>
   </si>
   <si>
@@ -686,7 +674,7 @@
     <t>6.8uH</t>
   </si>
   <si>
-    <t>0.25R</t>
+    <t>25m</t>
   </si>
   <si>
     <t>1K</t>
@@ -737,7 +725,7 @@
     <t>http://www.yageo.com/documents/recent/UPY-GPHC_X5R_4V-to-50V_12.pdf?src-supplier=Avnet+Europe</t>
   </si>
   <si>
-    <t>http://www.yageo.com/documents/recent/UPY-GP_NP0_16V-to-50V_16.pdf?src-supplier=Digi-Key, https://datasheet.ciiva.com/26862/getdatasheetpartid-639817-26862638.pdf?src-supplier=Verical</t>
+    <t>https://datasheet.ciiva.com/26862/getdatasheetpartid-639817-26862638.pdf?src-supplier=Verical</t>
   </si>
   <si>
     <t>https://datasheet.ciiva.com/170/product-170100.pdf?src-supplier=Digi-Key</t>
@@ -755,6 +743,9 @@
     <t>https://lcsc.com/product-detail/FFC-FPC-Connectors_XFCN-F0504-H-22-20T-R_C557729.html</t>
   </si>
   <si>
+    <t>http://www.farnell.com/cad/1737268.pdf?src-supplier=Element14</t>
+  </si>
+  <si>
     <t>https://www.hirose.com/product/en/download_file/key_name/FH34SRJ/category/Catalog/doc_file_id/31646/?file_category_id=4&amp;item_id=27&amp;is_series=1&amp;src-supplier=Digi-Key</t>
   </si>
   <si>
@@ -782,7 +773,10 @@
     <t>http://www.sunledusa.com/products/spec/XZMDK68W-2.pdf?src-supplier=Digi-Key</t>
   </si>
   <si>
-    <t>https://industrial.panasonic.com/cdbs/www-data/pdf/RDA0000/AOA0000C301.pdf?src-supplier=Future+Electronics, https://datasheet.ciiva.com/7983/1018594-7983558.pdf?src-supplier=Element14</t>
+    <t>https://lcsc.com/product-detail/Chip-Resistor-Surface-Mount_UNI-ROYAL-Uniroyal-Elec-0805W8F250MT5E_C620515.html</t>
+  </si>
+  <si>
+    <t>https://datasheet.ciiva.com/7983/1018594-7983558.pdf?src-supplier=Element14</t>
   </si>
   <si>
     <t>http://www.farnell.com/datasheets/2167052.pdf?src-supplier=Element14</t>
@@ -828,6 +822,12 @@
   </si>
   <si>
     <t>Quantity</t>
+  </si>
+  <si>
+    <t>#Column Name Error:' Quantity (5 Boards)</t>
+  </si>
+  <si>
+    <t>#Column Name Error:' Remarks</t>
   </si>
 </sst>
 </file>
@@ -856,12 +856,6 @@
       <color indexed="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="13"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -953,8 +947,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -992,7 +993,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1059,21 +1060,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1094,17 +1080,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1149,16 +1124,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1167,13 +1138,13 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1182,8 +1153,53 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1194,23 +1210,43 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1219,141 +1255,157 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1382,16 +1434,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>10417</xdr:rowOff>
+      <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1419,8 +1471,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13315950" y="600967"/>
-          <a:ext cx="1714500" cy="1104008"/>
+          <a:off x="20059650" y="629542"/>
+          <a:ext cx="1857375" cy="1104008"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1696,1609 +1748,1793 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
     <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.42578125" customWidth="1"/>
-    <col min="10" max="10" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="22"/>
+      <c r="B1" s="19"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="45"/>
-    </row>
-    <row r="2" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H1" s="2"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+    </row>
+    <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="12" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="48" t="s">
+      <c r="D2" s="10"/>
+      <c r="E2" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="48"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="14" t="s">
+      <c r="B3" s="21"/>
+      <c r="C3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="49" t="s">
+      <c r="D3" s="12"/>
+      <c r="E3" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="46"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="52"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="14" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="50" t="s">
+      <c r="D4" s="12"/>
+      <c r="E4" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="6"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="47"/>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="53"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="14" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="51" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="47"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="53"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="47"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="22"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="53"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="47"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="23"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="53"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="47"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="26"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="53"/>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="F9" s="34" t="s">
+      <c r="C9" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="G9" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>202</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>229</v>
-      </c>
-      <c r="J9" s="35" t="s">
+      <c r="G9" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>225</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="M9" s="31" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="36">
+      <c r="B10" s="32">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="F10" s="37" t="s">
+      <c r="C10" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="G10" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="J10" s="38">
+      <c r="G10" s="39"/>
+      <c r="H10" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="I10" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="J10" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="K10" s="39">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="L10" s="39"/>
+      <c r="M10" s="45"/>
+    </row>
+    <row r="11" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="36">
+      <c r="B11" s="32">
         <f t="shared" ref="B11:B56" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" s="39" t="s">
+      <c r="C11" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="G11" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="I11" s="39" t="s">
-        <v>231</v>
-      </c>
-      <c r="J11" s="40">
+      <c r="G11" s="41"/>
+      <c r="H11" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="I11" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="J11" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="K11" s="41">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="L11" s="41"/>
+      <c r="M11" s="46"/>
+    </row>
+    <row r="12" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="36">
+      <c r="B12" s="32">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="F12" s="37" t="s">
+      <c r="C12" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="F12" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="G12" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>205</v>
-      </c>
-      <c r="I12" s="37" t="s">
-        <v>232</v>
-      </c>
-      <c r="J12" s="38">
+      <c r="G12" s="39"/>
+      <c r="H12" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="I12" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="J12" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="K12" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L12" s="39"/>
+      <c r="M12" s="45"/>
+    </row>
+    <row r="13" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="36">
+      <c r="B13" s="32">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="F13" s="39" t="s">
+      <c r="C13" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="G13" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="I13" s="39" t="s">
-        <v>233</v>
-      </c>
-      <c r="J13" s="40">
+      <c r="G13" s="41"/>
+      <c r="H13" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="I13" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="J13" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="K13" s="41">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L13" s="41"/>
+      <c r="M13" s="46"/>
+    </row>
+    <row r="14" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="36">
+      <c r="B14" s="32">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="F14" s="37" t="s">
+      <c r="C14" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="G14" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="I14" s="37"/>
-      <c r="J14" s="38">
+      <c r="G14" s="39"/>
+      <c r="H14" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="I14" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="L14" s="39"/>
+      <c r="M14" s="45"/>
+    </row>
+    <row r="15" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="36">
+      <c r="B15" s="32">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="F15" s="39" t="s">
+      <c r="C15" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="G15" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>208</v>
-      </c>
-      <c r="I15" s="39" t="s">
-        <v>234</v>
-      </c>
-      <c r="J15" s="40">
+      <c r="G15" s="41"/>
+      <c r="H15" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="I15" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="J15" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="K15" s="41">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="L15" s="41"/>
+      <c r="M15" s="46"/>
+    </row>
+    <row r="16" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="36">
+      <c r="B16" s="32">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="F16" s="37" t="s">
+      <c r="C16" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="G16" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="I16" s="37"/>
-      <c r="J16" s="38">
+      <c r="G16" s="39"/>
+      <c r="H16" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="I16" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="L16" s="39"/>
+      <c r="M16" s="45"/>
+    </row>
+    <row r="17" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="36">
+      <c r="B17" s="32">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="F17" s="39" t="s">
+      <c r="C17" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="42" t="s">
         <v>146</v>
       </c>
-      <c r="G17" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="H17" s="39" t="s">
-        <v>210</v>
-      </c>
-      <c r="I17" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="J17" s="40">
+      <c r="G17" s="41"/>
+      <c r="H17" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="I17" s="42" t="s">
+        <v>207</v>
+      </c>
+      <c r="J17" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="K17" s="41">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L17" s="41"/>
+      <c r="M17" s="46"/>
+    </row>
+    <row r="18" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="36">
+      <c r="B18" s="32">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="F18" s="37" t="s">
+      <c r="C18" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="G18" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="H18" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="I18" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="J18" s="38">
+      <c r="G18" s="39"/>
+      <c r="H18" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="I18" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="J18" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="K18" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+      <c r="L18" s="39"/>
+      <c r="M18" s="45"/>
+    </row>
+    <row r="19" spans="1:13" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="36">
+      <c r="B19" s="32">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F19" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="H19" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="I19" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="J19" s="40">
+      <c r="C19" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="I19" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="J19" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="K19" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="L19" s="41"/>
+      <c r="M19" s="46"/>
+    </row>
+    <row r="20" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="36">
+      <c r="B20" s="32">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="G20" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="J20" s="38">
+      <c r="C20" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="I20" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="J20" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="K20" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="L20" s="39"/>
+      <c r="M20" s="45"/>
+    </row>
+    <row r="21" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="36">
+      <c r="B21" s="32">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="F21" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="I21" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="J21" s="40">
+      <c r="C21" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="I21" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="J21" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="K21" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="L21" s="41"/>
+      <c r="M21" s="46"/>
+    </row>
+    <row r="22" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="36">
+      <c r="B22" s="32">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="F22" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="I22" s="37" t="s">
-        <v>240</v>
-      </c>
-      <c r="J22" s="38">
+      <c r="C22" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="I22" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="J22" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="K22" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="L22" s="39"/>
+      <c r="M22" s="45"/>
+    </row>
+    <row r="23" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="36">
+      <c r="B23" s="32">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="F23" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="G23" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="H23" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="I23" s="39"/>
-      <c r="J23" s="40">
+      <c r="C23" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="F23" s="42">
+        <v>61300811121</v>
+      </c>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="I23" s="42">
+        <v>61300811121</v>
+      </c>
+      <c r="J23" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="K23" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="L23" s="41"/>
+      <c r="M23" s="46"/>
+    </row>
+    <row r="24" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="36">
+      <c r="B24" s="32">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>241</v>
-      </c>
-      <c r="J24" s="38">
+      <c r="C24" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="I24" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="J24" s="39" t="s">
+        <v>238</v>
+      </c>
+      <c r="K24" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L24" s="39"/>
+      <c r="M24" s="45"/>
+    </row>
+    <row r="25" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="36">
+      <c r="B25" s="32">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="H25" s="39" t="s">
-        <v>212</v>
-      </c>
-      <c r="I25" s="39"/>
-      <c r="J25" s="40">
+      <c r="C25" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="42">
+        <v>61300411121</v>
+      </c>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="I25" s="42">
+        <v>61300411121</v>
+      </c>
+      <c r="J25" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="K25" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L25" s="41"/>
+      <c r="M25" s="46"/>
+    </row>
+    <row r="26" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="36">
+      <c r="B26" s="32">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="H26" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="I26" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="J26" s="38">
+      <c r="C26" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="J26" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="K26" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="L26" s="39"/>
+      <c r="M26" s="45"/>
+    </row>
+    <row r="27" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
-      <c r="B27" s="36">
+      <c r="B27" s="32">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="G27" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="H27" s="39" t="s">
-        <v>214</v>
-      </c>
-      <c r="I27" s="39" t="s">
-        <v>243</v>
-      </c>
-      <c r="J27" s="40">
+      <c r="C27" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="I27" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="J27" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="K27" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L27" s="41"/>
+      <c r="M27" s="46"/>
+    </row>
+    <row r="28" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="36">
+      <c r="B28" s="32">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="I28" s="37"/>
-      <c r="J28" s="38">
+      <c r="C28" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="F28" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="I28" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="L28" s="39"/>
+      <c r="M28" s="45"/>
+    </row>
+    <row r="29" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
-      <c r="B29" s="36">
+      <c r="B29" s="32">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="F29" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="G29" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="H29" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I29" s="39" t="s">
-        <v>244</v>
-      </c>
-      <c r="J29" s="40">
+      <c r="C29" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="I29" s="42" t="s">
+        <v>211</v>
+      </c>
+      <c r="J29" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="K29" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="L29" s="41"/>
+      <c r="M29" s="46"/>
+    </row>
+    <row r="30" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="B30" s="36">
+      <c r="B30" s="32">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="H30" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="J30" s="38">
+      <c r="C30" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="I30" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="J30" s="39" t="s">
+        <v>242</v>
+      </c>
+      <c r="K30" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="L30" s="39"/>
+      <c r="M30" s="45"/>
+    </row>
+    <row r="31" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="36">
+      <c r="B31" s="32">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="E31" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="F31" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="H31" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="I31" s="39" t="s">
-        <v>246</v>
-      </c>
-      <c r="J31" s="40">
+      <c r="C31" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="I31" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="J31" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="K31" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="L31" s="41"/>
+      <c r="M31" s="46"/>
+    </row>
+    <row r="32" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="B32" s="36">
+      <c r="B32" s="32">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>217</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="J32" s="38">
+      <c r="C32" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="F32" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="I32" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="J32" s="39" t="s">
+        <v>244</v>
+      </c>
+      <c r="K32" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L32" s="39"/>
+      <c r="M32" s="45"/>
+    </row>
+    <row r="33" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
-      <c r="B33" s="36">
+      <c r="B33" s="32">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="E33" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="G33" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="H33" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="I33" s="39" t="s">
-        <v>248</v>
-      </c>
-      <c r="J33" s="40">
+      <c r="C33" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F33" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="I33" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="J33" s="41" t="s">
+        <v>245</v>
+      </c>
+      <c r="K33" s="41">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L33" s="41"/>
+      <c r="M33" s="46"/>
+    </row>
+    <row r="34" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="B34" s="36">
+      <c r="B34" s="32">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="G34" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="J34" s="38">
+      <c r="C34" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39" t="s">
+        <v>183</v>
+      </c>
+      <c r="I34" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="J34" s="39" t="s">
+        <v>246</v>
+      </c>
+      <c r="K34" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="L34" s="39"/>
+      <c r="M34" s="45"/>
+    </row>
+    <row r="35" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="36">
+      <c r="B35" s="32">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="E35" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="F35" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="G35" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="H35" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="I35" s="39"/>
-      <c r="J35" s="40">
+      <c r="C35" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="E35" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="F35" s="42"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="I35" s="42" t="s">
+        <v>214</v>
+      </c>
+      <c r="J35" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="K35" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+      <c r="L35" s="41"/>
+      <c r="M35" s="46"/>
+    </row>
+    <row r="36" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="36">
+      <c r="B36" s="32">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="E36" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="G36" s="37" t="s">
-        <v>187</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>250</v>
-      </c>
-      <c r="J36" s="38">
+      <c r="C36" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="F36" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="I36" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="J36" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="K36" s="39">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L36" s="39"/>
+      <c r="M36" s="45"/>
+    </row>
+    <row r="37" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="36">
+      <c r="B37" s="32">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="E37" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="F37" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="G37" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="H37" s="39" t="s">
-        <v>220</v>
-      </c>
-      <c r="I37" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="J37" s="40">
+      <c r="C37" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="I37" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="J37" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="K37" s="41">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="L37" s="41"/>
+      <c r="M37" s="46"/>
+    </row>
+    <row r="38" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="B38" s="36">
+      <c r="B38" s="32">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="E38" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="G38" s="37" t="s">
-        <v>188</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="J38" s="38">
+      <c r="C38" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="E38" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="F38" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="I38" s="40" t="s">
+        <v>217</v>
+      </c>
+      <c r="J38" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="K38" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L38" s="39"/>
+      <c r="M38" s="45"/>
+    </row>
+    <row r="39" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="36">
+      <c r="B39" s="32">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="E39" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="F39" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="G39" s="39" t="s">
-        <v>189</v>
-      </c>
-      <c r="H39" s="39" t="s">
-        <v>222</v>
-      </c>
-      <c r="I39" s="39" t="s">
-        <v>253</v>
-      </c>
-      <c r="J39" s="40">
+      <c r="C39" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="E39" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="F39" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="G39" s="41"/>
+      <c r="H39" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="I39" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="J39" s="41" t="s">
+        <v>251</v>
+      </c>
+      <c r="K39" s="41">
         <v>7</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="L39" s="41"/>
+      <c r="M39" s="46"/>
+    </row>
+    <row r="40" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="36">
+      <c r="B40" s="32">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="J40" s="38">
+      <c r="C40" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="F40" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="G40" s="39"/>
+      <c r="H40" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="I40" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="J40" s="39" t="s">
+        <v>252</v>
+      </c>
+      <c r="K40" s="39">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L40" s="39"/>
+      <c r="M40" s="45"/>
+    </row>
+    <row r="41" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="36">
+      <c r="B41" s="32">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="E41" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="F41" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="G41" s="39" t="s">
-        <v>190</v>
-      </c>
-      <c r="H41" s="39" t="s">
-        <v>224</v>
-      </c>
-      <c r="I41" s="39" t="s">
-        <v>255</v>
-      </c>
-      <c r="J41" s="40">
+      <c r="C41" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="E41" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="F41" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="G41" s="41"/>
+      <c r="H41" s="41" t="s">
+        <v>187</v>
+      </c>
+      <c r="I41" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="J41" s="41" t="s">
+        <v>253</v>
+      </c>
+      <c r="K41" s="41">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L41" s="41"/>
+      <c r="M41" s="46"/>
+    </row>
+    <row r="42" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="36">
+      <c r="B42" s="32">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E42" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="G42" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="H42" s="37" t="s">
-        <v>225</v>
-      </c>
-      <c r="I42" s="37"/>
-      <c r="J42" s="38">
+      <c r="C42" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="F42" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="G42" s="39"/>
+      <c r="H42" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="I42" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="J42" s="39"/>
+      <c r="K42" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L42" s="39"/>
+      <c r="M42" s="45"/>
+    </row>
+    <row r="43" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="B43" s="36">
+      <c r="B43" s="32">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D43" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="E43" s="39" t="s">
+      <c r="C43" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="E43" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="F43" s="39"/>
-      <c r="G43" s="39"/>
-      <c r="H43" s="39" t="s">
+      <c r="F43" s="42"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="I43" s="39"/>
-      <c r="J43" s="40">
+      <c r="J43" s="41"/>
+      <c r="K43" s="41">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="L43" s="41"/>
+      <c r="M43" s="46"/>
+    </row>
+    <row r="44" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
-      <c r="B44" s="36">
+      <c r="B44" s="32">
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="D44" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E44" s="37" t="s">
+      <c r="C44" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="E44" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="F44" s="37" t="s">
+      <c r="F44" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="G44" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="H44" s="37" t="s">
+      <c r="G44" s="39"/>
+      <c r="H44" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="I44" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="I44" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="J44" s="38">
+      <c r="J44" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="K44" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="L44" s="39"/>
+      <c r="M44" s="45"/>
+    </row>
+    <row r="45" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
-      <c r="B45" s="36">
+      <c r="B45" s="32">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="E45" s="39" t="s">
+      <c r="C45" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="F45" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="G45" s="39" t="s">
-        <v>192</v>
-      </c>
-      <c r="H45" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="I45" s="39"/>
-      <c r="J45" s="40">
+      <c r="F45" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="I45" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="J45" s="41"/>
+      <c r="K45" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L45" s="41"/>
+      <c r="M45" s="46"/>
+    </row>
+    <row r="46" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
-      <c r="B46" s="36">
+      <c r="B46" s="32">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E46" s="37" t="s">
+      <c r="C46" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="E46" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="F46" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="G46" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="H46" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="I46" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="J46" s="38">
+      <c r="F46" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="G46" s="39"/>
+      <c r="H46" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="I46" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="J46" s="39" t="s">
+        <v>255</v>
+      </c>
+      <c r="K46" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L46" s="39"/>
+      <c r="M46" s="45"/>
+    </row>
+    <row r="47" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
-      <c r="B47" s="36">
+      <c r="B47" s="32">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D47" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="E47" s="39" t="s">
+      <c r="C47" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="E47" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="F47" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="G47" s="39" t="s">
-        <v>194</v>
-      </c>
-      <c r="H47" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="I47" s="39" t="s">
-        <v>258</v>
-      </c>
-      <c r="J47" s="40">
+      <c r="F47" s="42" t="s">
+        <v>162</v>
+      </c>
+      <c r="G47" s="41"/>
+      <c r="H47" s="41" t="s">
+        <v>191</v>
+      </c>
+      <c r="I47" s="42" t="s">
+        <v>162</v>
+      </c>
+      <c r="J47" s="41" t="s">
+        <v>256</v>
+      </c>
+      <c r="K47" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="L47" s="41"/>
+      <c r="M47" s="46"/>
+    </row>
+    <row r="48" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
-      <c r="B48" s="36">
+      <c r="B48" s="32">
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E48" s="37" t="s">
+      <c r="C48" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="D48" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="E48" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="F48" s="37" t="s">
-        <v>165</v>
-      </c>
-      <c r="G48" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="H48" s="37" t="s">
-        <v>165</v>
-      </c>
-      <c r="I48" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J48" s="38">
+      <c r="F48" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="G48" s="39"/>
+      <c r="H48" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="I48" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="J48" s="39" t="s">
+        <v>257</v>
+      </c>
+      <c r="K48" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="L48" s="39"/>
+      <c r="M48" s="45"/>
+    </row>
+    <row r="49" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
-      <c r="B49" s="36">
+      <c r="B49" s="32">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="D49" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="E49" s="39" t="s">
+      <c r="C49" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="E49" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="F49" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="G49" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="H49" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="I49" s="39" t="s">
-        <v>260</v>
-      </c>
-      <c r="J49" s="40">
+      <c r="F49" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="I49" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="J49" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="K49" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="L49" s="41"/>
+      <c r="M49" s="46"/>
+    </row>
+    <row r="50" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
-      <c r="B50" s="36">
+      <c r="B50" s="32">
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
-      <c r="C50" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="D50" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E50" s="37" t="s">
+      <c r="C50" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="D50" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="E50" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="F50" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="G50" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="H50" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="I50" s="37"/>
-      <c r="J50" s="38">
+      <c r="F50" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="G50" s="39"/>
+      <c r="H50" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="I50" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="J50" s="39"/>
+      <c r="K50" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="L50" s="39"/>
+      <c r="M50" s="45"/>
+    </row>
+    <row r="51" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
-      <c r="B51" s="36">
+      <c r="B51" s="32">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="D51" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E51" s="39" t="s">
+      <c r="C51" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="D51" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="E51" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="F51" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="G51" s="39" t="s">
-        <v>198</v>
-      </c>
-      <c r="H51" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="I51" s="39" t="s">
-        <v>261</v>
-      </c>
-      <c r="J51" s="40">
+      <c r="F51" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="G51" s="41"/>
+      <c r="H51" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="I51" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="J51" s="41" t="s">
+        <v>259</v>
+      </c>
+      <c r="K51" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="L51" s="41"/>
+      <c r="M51" s="46"/>
+    </row>
+    <row r="52" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
-      <c r="B52" s="36">
+      <c r="B52" s="32">
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
-      <c r="C52" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="D52" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="E52" s="37" t="s">
+      <c r="C52" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="D52" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="E52" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="F52" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="G52" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="H52" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="I52" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="J52" s="38">
+      <c r="F52" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="G52" s="39"/>
+      <c r="H52" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="I52" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="J52" s="39" t="s">
+        <v>260</v>
+      </c>
+      <c r="K52" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="L52" s="39"/>
+      <c r="M52" s="45"/>
+    </row>
+    <row r="53" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
-      <c r="B53" s="36">
+      <c r="B53" s="32">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="D53" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="E53" s="39" t="s">
+      <c r="C53" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="D53" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="E53" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="F53" s="39" t="s">
+      <c r="F53" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="G53" s="39" t="s">
-        <v>200</v>
-      </c>
-      <c r="H53" s="39" t="s">
-        <v>226</v>
-      </c>
-      <c r="I53" s="39" t="s">
-        <v>263</v>
-      </c>
-      <c r="J53" s="40">
+      <c r="G53" s="41"/>
+      <c r="H53" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="I53" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="J53" s="41" t="s">
+        <v>261</v>
+      </c>
+      <c r="K53" s="41">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="L53" s="41"/>
+      <c r="M53" s="46"/>
+    </row>
+    <row r="54" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
-      <c r="B54" s="36">
+      <c r="B54" s="32">
         <f>ROW(B54) - ROW($B$9)</f>
         <v>45</v>
       </c>
-      <c r="C54" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="D54" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="E54" s="37" t="s">
+      <c r="C54" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="E54" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="F54" s="37" t="s">
+      <c r="F54" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="G54" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="H54" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="I54" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="J54" s="38">
+      <c r="G54" s="39"/>
+      <c r="H54" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="I54" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="J54" s="39" t="s">
+        <v>262</v>
+      </c>
+      <c r="K54" s="39">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="L54" s="39"/>
+      <c r="M54" s="45"/>
+    </row>
+    <row r="55" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
-      <c r="B55" s="36">
+      <c r="B55" s="32">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="D55" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="E55" s="39" t="s">
+      <c r="C55" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="E55" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="F55" s="39" t="s">
+      <c r="F55" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="G55" s="39" t="s">
-        <v>201</v>
-      </c>
-      <c r="H55" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="I55" s="39"/>
-      <c r="J55" s="40">
+      <c r="G55" s="41"/>
+      <c r="H55" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="I55" s="42" t="s">
+        <v>224</v>
+      </c>
+      <c r="J55" s="41"/>
+      <c r="K55" s="41">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L55" s="41"/>
+      <c r="M55" s="46"/>
+    </row>
+    <row r="56" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
-      <c r="B56" s="36">
+      <c r="B56" s="33">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C56" s="39"/>
-      <c r="D56" s="39"/>
-      <c r="E56" s="39"/>
-      <c r="F56" s="39"/>
-      <c r="G56" s="39"/>
-      <c r="H56" s="39"/>
-      <c r="I56" s="39"/>
-      <c r="J56" s="40"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C56" s="43"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="43"/>
+      <c r="F56" s="44"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="43"/>
+      <c r="I56" s="44"/>
+      <c r="J56" s="43"/>
+      <c r="K56" s="43"/>
+      <c r="L56" s="43"/>
+      <c r="M56" s="47"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="B57" s="32"/>
-      <c r="C57" s="30" t="s">
+      <c r="B57" s="34"/>
+      <c r="C57" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D57" s="31"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="42"/>
-      <c r="I57" s="42"/>
-      <c r="J57" s="52" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D57" s="36"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="38"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="37"/>
+      <c r="I57" s="38"/>
+      <c r="J57" s="38"/>
+      <c r="K57" s="38"/>
+      <c r="L57" s="38"/>
+      <c r="M57" s="49"/>
+    </row>
+    <row r="58" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="10" t="s">
+      <c r="B58" s="24"/>
+      <c r="C58" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11"/>
-      <c r="J58" s="43"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+      <c r="M58" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="J3:J8"/>
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="M3:M8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
